--- a/reports/latest/Portfolio_Report.xlsx
+++ b/reports/latest/Portfolio_Report.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR3"/>
+  <dimension ref="A1:BR2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1020,12 +1020,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1039,134 +1039,138 @@
         </is>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
       <c r="G2" s="1" t="n">
-        <v>43566</v>
+        <v>43101</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46022</v>
+        <v>46203</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="J2" t="n">
-        <v>561</v>
+        <v>619</v>
       </c>
       <c r="K2" t="n">
-        <v>46.2</v>
+        <v>50.4</v>
       </c>
       <c r="L2" t="n">
-        <v>46.2</v>
+        <v>50.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.47</v>
+        <v>2.24</v>
       </c>
       <c r="N2" t="n">
-        <v>3.47</v>
+        <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>13.61</v>
+        <v>8.75</v>
       </c>
       <c r="P2" t="n">
-        <v>-5.22</v>
+        <v>-4.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>20.87</v>
+        <v>11.92</v>
       </c>
       <c r="S2" t="n">
-        <v>0.476</v>
+        <v>0.248</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="V2" t="n">
-        <v>1946.82</v>
+        <v>1385.36</v>
       </c>
       <c r="W2" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="X2" t="n">
-        <v>2.61</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>-21.56</v>
+        <v>-14.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>-82.89</v>
+        <v>-80.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.95</v>
+        <v>-0.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.57</v>
+        <v>53.01</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.57</v>
+        <v>53.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>24.05</v>
+        <v>17.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.86</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="b">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>356.13</v>
+        <v>1517.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.67</v>
+        <v>2.51</v>
       </c>
       <c r="AK2" t="n">
-        <v>356.13</v>
+        <v>1517.4</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>356.13</v>
+        <v>1517.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>330</v>
+        <v>1441.16</v>
       </c>
       <c r="AO2" t="n">
-        <v>-7.34</v>
+        <v>-5.02</v>
       </c>
       <c r="AP2" t="n">
-        <v>391.74</v>
+        <v>1669.14</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="AS2" t="n">
-        <v>39.6</v>
+        <v>32.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AU2" t="n">
-        <v>53.7</v>
+        <v>48.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.8</v>
+        <v>18.7</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>limited history: 6.7y (&lt;10y) - lower confidence</t>
+          <t>limited history: 8.5y (&lt;10y) - lower confidence</t>
         </is>
       </c>
       <c r="BB2" t="n">
@@ -1192,37 +1196,37 @@
         <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
         <v>1</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.7499999999999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>1</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -1230,243 +1234,15 @@
         </is>
       </c>
       <c r="BP2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>20260726_212606</t>
+          <t>20260727_155757</t>
         </is>
       </c>
       <c r="BR2" s="2" t="n">
-        <v>46229.89312574888</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>UPTREND</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>43101</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>553</v>
-      </c>
-      <c r="K3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O3" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-4.47</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>93</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1170.86</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-15.82</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-80.69</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1106.9</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1106.9</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>1106.9</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1061.81</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-4.07</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1217.59</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>14d</t>
-        </is>
-      </c>
-      <c r="AR3" t="n">
-        <v>179</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>281</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>limited history: 8.0y (&lt;10y) - lower confidence</t>
-        </is>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="BP3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>20260726_212606</t>
-        </is>
-      </c>
-      <c r="BR3" s="2" t="n">
-        <v>46229.89312574888</v>
+        <v>46230.66525462313</v>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1566,7 +1342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1576,7 +1352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1626,7 +1402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1636,7 +1412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -1688,7 +1464,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1698,7 +1474,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1718,7 +1494,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10004576.158185</v>
+        <v>10004665.833</v>
       </c>
     </row>
     <row r="6">
@@ -1728,7 +1504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.0004576158185</v>
+        <v>1.0004665833</v>
       </c>
     </row>
     <row r="7">
@@ -1738,7 +1514,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10502.30507200128</v>
+        <v>10502.39920814909</v>
       </c>
     </row>
     <row r="8">
@@ -1748,7 +1524,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4999.788184999529</v>
+        <v>4999.832999999094</v>
       </c>
     </row>
     <row r="9">
@@ -1768,7 +1544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1778,7 +1554,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5002288.0790925</v>
+        <v>10004665.833</v>
       </c>
     </row>
     <row r="12">
@@ -1788,7 +1564,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9278</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="13">
@@ -1798,7 +1574,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>731.8807575</v>
+        <v>1518.1587</v>
       </c>
     </row>
     <row r="14">
@@ -1808,7 +1584,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9989502498750624</v>
+        <v>0.9989502498750625</v>
       </c>
     </row>
     <row r="15">
@@ -1869,7 +1645,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26 21:26:06.084017</t>
+          <t>2026-07-27 15:57:58.028050</t>
         </is>
       </c>
     </row>
